--- a/public/data/Mill Shutdown March 2026.xlsx
+++ b/public/data/Mill Shutdown March 2026.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11280FB9-448D-4A5C-B400-8AD1C0BD7075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{379B16FA-B4C0-4C9D-8181-6F44DC2A7D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13679" uniqueCount="2915">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13742" uniqueCount="2915">
   <si>
     <t xml:space="preserve">Date
 </t>
@@ -9082,7 +9082,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
@@ -9256,6 +9256,12 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -28334,7 +28340,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M320"/>
+  <dimension ref="A1:M324"/>
   <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
@@ -29111,6 +29117,15 @@
       <c r="F23"/>
       <c r="G23" s="42"/>
       <c r="H23" s="29"/>
+      <c r="J23" t="s">
+        <v>2741</v>
+      </c>
+      <c r="K23" s="62">
+        <v>4700022233</v>
+      </c>
+      <c r="L23">
+        <v>10</v>
+      </c>
       <c r="M23" s="29"/>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.35">
@@ -34384,6 +34399,74 @@
         <v>2891</v>
       </c>
       <c r="E320" s="47">
+        <v>3001496</v>
+      </c>
+    </row>
+    <row r="321" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A321" s="48" t="s">
+        <v>2741</v>
+      </c>
+      <c r="B321" s="48" t="s">
+        <v>2612</v>
+      </c>
+      <c r="C321" s="29">
+        <v>90303174</v>
+      </c>
+      <c r="D321" s="48" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E321" s="47">
+        <v>3001496</v>
+      </c>
+    </row>
+    <row r="322" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A322" s="48" t="s">
+        <v>2741</v>
+      </c>
+      <c r="B322" s="48" t="s">
+        <v>2613</v>
+      </c>
+      <c r="C322" s="29">
+        <v>90303174</v>
+      </c>
+      <c r="D322" s="48" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E322" s="47">
+        <v>3001496</v>
+      </c>
+    </row>
+    <row r="323" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A323" s="48" t="s">
+        <v>2741</v>
+      </c>
+      <c r="B323" s="48" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C323" s="29">
+        <v>90303175</v>
+      </c>
+      <c r="D323" s="48" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E323" s="47">
+        <v>3001496</v>
+      </c>
+    </row>
+    <row r="324" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A324" s="48" t="s">
+        <v>2741</v>
+      </c>
+      <c r="B324" s="48" t="s">
+        <v>2615</v>
+      </c>
+      <c r="C324" s="29">
+        <v>90303175</v>
+      </c>
+      <c r="D324" s="48" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E324" s="47">
         <v>3001496</v>
       </c>
     </row>
@@ -34411,7 +34494,7 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:H2050"/>
+  <dimension ref="A1:H2060"/>
   <sheetFormatPr defaultColWidth="18.453125" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" customWidth="1"/>
@@ -75403,6 +75486,206 @@
         <v>132</v>
       </c>
     </row>
+    <row r="2051" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2051" s="42">
+        <v>15907437</v>
+      </c>
+      <c r="B2051" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2051" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2051" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2051" s="33" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F2051" s="38" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2052" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2052" s="42">
+        <v>16340682</v>
+      </c>
+      <c r="B2052" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2052" t="s">
+        <v>472</v>
+      </c>
+      <c r="D2052" t="s">
+        <v>479</v>
+      </c>
+      <c r="E2052" s="33" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F2052" s="38" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2053" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2053" s="42">
+        <v>16342622</v>
+      </c>
+      <c r="B2053" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="C2053" t="s">
+        <v>518</v>
+      </c>
+      <c r="D2053" t="s">
+        <v>523</v>
+      </c>
+      <c r="E2053" s="33" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F2053" s="38" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2054" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2054" s="42">
+        <v>16342622</v>
+      </c>
+      <c r="B2054" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="C2054" t="s">
+        <v>518</v>
+      </c>
+      <c r="D2054" t="s">
+        <v>534</v>
+      </c>
+      <c r="E2054" s="33" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F2054" s="38" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2055" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2055" s="42">
+        <v>16346271</v>
+      </c>
+      <c r="B2055" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2055" s="61" t="s">
+        <v>610</v>
+      </c>
+      <c r="D2055" t="s">
+        <v>611</v>
+      </c>
+      <c r="E2055" s="33" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F2055" s="38" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2056" s="42">
+        <v>16347752</v>
+      </c>
+      <c r="B2056" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2056" t="s">
+        <v>708</v>
+      </c>
+      <c r="D2056" t="s">
+        <v>709</v>
+      </c>
+      <c r="E2056" s="33" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F2056" s="38" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2057" s="42">
+        <v>16351590</v>
+      </c>
+      <c r="B2057" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2057" t="s">
+        <v>1419</v>
+      </c>
+      <c r="D2057" t="s">
+        <v>1282</v>
+      </c>
+      <c r="E2057" s="33" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F2057" s="38" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2058" s="42">
+        <v>16360953</v>
+      </c>
+      <c r="B2058" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2058" t="s">
+        <v>1998</v>
+      </c>
+      <c r="D2058" t="s">
+        <v>1999</v>
+      </c>
+      <c r="E2058" s="33" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F2058" s="38" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2059" s="42">
+        <v>16361858</v>
+      </c>
+      <c r="B2059" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2059" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D2059" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E2059" s="33" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F2059" s="38" t="s">
+        <v>2741</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2060" s="42">
+        <v>16364295</v>
+      </c>
+      <c r="B2060" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2060" t="s">
+        <v>2187</v>
+      </c>
+      <c r="D2060" t="s">
+        <v>2190</v>
+      </c>
+      <c r="E2060" s="33" t="s">
+        <v>2874</v>
+      </c>
+      <c r="F2060" s="38" t="s">
+        <v>2741</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F2050" xr:uid="{00000000-0009-0000-0000-000004000000}">
     <filterColumn colId="5">

--- a/public/data/Mill Shutdown March 2026.xlsx
+++ b/public/data/Mill Shutdown March 2026.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F3DF13D-E94A-430A-A622-7F722D272282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B5D31DF-0C4E-443F-8C58-9C8F52046314}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Vendor Entry Sheet" sheetId="5" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13742" uniqueCount="2913">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13777" uniqueCount="2922">
   <si>
     <t xml:space="preserve">Date
 </t>
@@ -8835,6 +8835,33 @@
   </si>
   <si>
     <t>BoltPrep</t>
+  </si>
+  <si>
+    <t>T1ML001 SAG Shell Bolts Insp</t>
+  </si>
+  <si>
+    <t>Ball Mill Bolt Insp</t>
+  </si>
+  <si>
+    <t>Ball Mill Girth Gear Inspection</t>
+  </si>
+  <si>
+    <t>Kenneth Gray</t>
+  </si>
+  <si>
+    <t>Darren Lee</t>
+  </si>
+  <si>
+    <t>Paul Sant</t>
+  </si>
+  <si>
+    <t>Kalen Di Re</t>
+  </si>
+  <si>
+    <t>Elia Giller</t>
+  </si>
+  <si>
+    <t>Richard Hittmann</t>
   </si>
 </sst>
 </file>
@@ -28334,7 +28361,7 @@
   <sheetPr>
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:M324"/>
+  <dimension ref="A1:M330"/>
   <sheetFormatPr defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="24.1796875" bestFit="1" customWidth="1"/>
@@ -29141,6 +29168,9 @@
       <c r="F24"/>
       <c r="G24" s="42"/>
       <c r="H24" s="29"/>
+      <c r="J24" t="s">
+        <v>2437</v>
+      </c>
       <c r="M24" s="29"/>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.35">
@@ -34461,6 +34491,108 @@
         <v>2494</v>
       </c>
       <c r="E324" s="47">
+        <v>3001496</v>
+      </c>
+    </row>
+    <row r="325" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A325" s="48" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B325" s="48" t="s">
+        <v>2916</v>
+      </c>
+      <c r="C325" s="29">
+        <v>90302832</v>
+      </c>
+      <c r="D325" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E325" s="47">
+        <v>3001496</v>
+      </c>
+    </row>
+    <row r="326" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A326" s="48" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B326" s="48" t="s">
+        <v>2917</v>
+      </c>
+      <c r="C326" s="29">
+        <v>90301944</v>
+      </c>
+      <c r="D326" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E326" s="47">
+        <v>3001496</v>
+      </c>
+    </row>
+    <row r="327" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A327" s="48" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B327" s="48" t="s">
+        <v>2918</v>
+      </c>
+      <c r="C327" s="29">
+        <v>90302833</v>
+      </c>
+      <c r="D327" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E327" s="47">
+        <v>3001496</v>
+      </c>
+    </row>
+    <row r="328" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A328" s="48" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B328" s="48" t="s">
+        <v>2919</v>
+      </c>
+      <c r="C328" s="29">
+        <v>90302834</v>
+      </c>
+      <c r="D328" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E328" s="47">
+        <v>3001496</v>
+      </c>
+    </row>
+    <row r="329" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A329" s="48" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B329" s="48" t="s">
+        <v>2920</v>
+      </c>
+      <c r="C329" s="29">
+        <v>90300076</v>
+      </c>
+      <c r="D329" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E329" s="47">
+        <v>3001496</v>
+      </c>
+    </row>
+    <row r="330" spans="1:5" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A330" s="48" t="s">
+        <v>2437</v>
+      </c>
+      <c r="B330" s="48" t="s">
+        <v>2921</v>
+      </c>
+      <c r="C330" s="29">
+        <v>90302835</v>
+      </c>
+      <c r="D330" s="48" t="s">
+        <v>114</v>
+      </c>
+      <c r="E330" s="47">
         <v>3001496</v>
       </c>
     </row>
@@ -34488,7 +34620,7 @@
   <sheetPr filterMode="1">
     <tabColor rgb="FF00B050"/>
   </sheetPr>
-  <dimension ref="A1:H2060"/>
+  <dimension ref="A1:H2064"/>
   <sheetFormatPr defaultColWidth="18.453125" defaultRowHeight="14.5" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="18.7265625" customWidth="1"/>
@@ -75680,6 +75812,86 @@
         <v>2741</v>
       </c>
     </row>
+    <row r="2061" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2061" s="42">
+        <v>16347088</v>
+      </c>
+      <c r="B2061" s="42">
+        <v>10</v>
+      </c>
+      <c r="C2061" s="33" t="s">
+        <v>2913</v>
+      </c>
+      <c r="D2061" s="33" t="s">
+        <v>487</v>
+      </c>
+      <c r="E2061" s="33" t="s">
+        <v>2875</v>
+      </c>
+      <c r="F2061" s="38" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2062" s="42">
+        <v>16342163</v>
+      </c>
+      <c r="B2062" s="42">
+        <v>40</v>
+      </c>
+      <c r="C2062" s="33" t="s">
+        <v>487</v>
+      </c>
+      <c r="D2062" s="33" t="s">
+        <v>487</v>
+      </c>
+      <c r="E2062" s="33" t="s">
+        <v>2875</v>
+      </c>
+      <c r="F2062" s="38" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2063" s="42">
+        <v>16356571</v>
+      </c>
+      <c r="B2063" s="42">
+        <v>30</v>
+      </c>
+      <c r="C2063" s="33" t="s">
+        <v>2914</v>
+      </c>
+      <c r="D2063" s="33" t="s">
+        <v>2914</v>
+      </c>
+      <c r="E2063" s="33" t="s">
+        <v>2875</v>
+      </c>
+      <c r="F2063" s="38" t="s">
+        <v>2437</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:6" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2064" s="42">
+        <v>16351644</v>
+      </c>
+      <c r="B2064" s="42">
+        <v>60</v>
+      </c>
+      <c r="C2064" s="33" t="s">
+        <v>2915</v>
+      </c>
+      <c r="D2064" s="33" t="s">
+        <v>2915</v>
+      </c>
+      <c r="E2064" s="33" t="s">
+        <v>2875</v>
+      </c>
+      <c r="F2064" s="38" t="s">
+        <v>2437</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F2060" xr:uid="{00000000-0009-0000-0000-000004000000}">
     <filterColumn colId="5">
